--- a/assets/factor/practice/Regression Questions - Categorical Problem Set 5.xlsx
+++ b/assets/factor/practice/Regression Questions - Categorical Problem Set 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\4 Factor Models\3 Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036BF25A-73B3-45A0-983D-90CF7A986C13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52275B39-DAB6-4304-9475-5E28731E36F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{6966A72F-87B1-4C64-918B-9AD96792B0E2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{6966A72F-87B1-4C64-918B-9AD96792B0E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data- Start Here" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>Given a market return, you suspect that Apple's alpha is lower on Mondays compared to the rest of the week.</t>
   </si>
   <si>
-    <t>Estimate a model where Apple's y-intercept is allowed to vary based on if the trading day is either Monday or the rest of week.</t>
-  </si>
-  <si>
     <t>Using an F-test, test if Apple's alpha on Monday is statistically significantly different.</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>Fail to teject null. Monday's alpha not different</t>
+  </si>
+  <si>
+    <t>Estimate a model where Apple's alpha is allowed to vary based on if the trading day is either Monday or the rest of week.</t>
   </si>
 </sst>
 </file>
@@ -964,7 +964,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
@@ -974,7 +974,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1005,7 @@
         <v>26</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="19" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="6">
         <v>8.4386785609954426E-2</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="9">
         <f>B17</f>
@@ -2072,7 +2072,7 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <f>'Regression without Indicator'!C13</f>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <f>'Regression with Indicator'!C13</f>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <f>'Regression with Indicator'!D13</f>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>30</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <f>(B2-B4)/(B9*B5)</f>
@@ -2132,14 +2132,14 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <f>1-_xlfn.F.DIST(B11,B9,B7-(B8+1),TRUE)</f>
         <v>0.81856084204937807</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
